--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0661D69-D451-4CE9-8E00-502128679C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA60CCA0-BB18-48D0-AFC3-E2B2A60BBBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,13 +723,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S03aH04,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S04aH03,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S03aH03,S04aH05,S04aH08,S03aH02</t>
+    <t>S03aH02,S04aH02,S04aH03,S04aH05,S04aH08,S04aH06,S02aH02,S01aH06,S02aH03,S03aH04,S03aH03,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S02aH09,S04aH09,S03aH09,S03aH08,S03aH10,S04aH08,S02aH01,S02aH10,S01aH01,S04aH01,S01aH02,S03aH01,S01aH08,S02aH08,S01aH09,S02aH02,S04aH10,S04aH02</t>
+    <t>S04aH02,S01aH10,S03aH02,S04aH08,S02aH01,S02aH10,S03aH01,S01aH01,S04aH01,S02aH09,S04aH09,S02aH02,S04aH10,S03aH08,S03aH10,S03aH09,S01aH09,S01aH08,S02aH08,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S02aH09,S04aH09,S03aH09,S03aH08,S03aH10,S04aH08,S02aH01,S02aH10,S01aH01,S04aH01,S01aH02,S03aH01,S01aH08,S02aH08,S01aH09,S02aH02,S04aH10,S04aH02</v>
+        <v>S04aH02,S01aH10,S03aH02,S04aH08,S02aH01,S02aH10,S03aH01,S01aH01,S04aH01,S02aH09,S04aH09,S02aH02,S04aH10,S03aH08,S03aH10,S03aH09,S01aH09,S01aH08,S02aH08,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH02,S03aH04,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S04aH03,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S03aH03,S04aH05,S04aH08,S03aH02</v>
+        <v>S03aH02,S04aH02,S04aH03,S04aH05,S04aH08,S04aH06,S02aH02,S01aH06,S02aH03,S03aH04,S03aH03,S02aH04,S02aH05,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1452,7 +1452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F918DB5D-F0F1-4819-AD2C-A8E8B792D85B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB22A7F-0763-4E2F-B42B-4314344B827E}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1590,7 +1590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5528B728-4993-4589-B9C3-457254BEA8E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBADF41-EFF0-491A-B19D-EFE8EA7D7E05}">
   <dimension ref="B9:O970"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30932,7 +30932,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA63F0F-ED9B-4AD6-9728-91AAB9F96EC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FADAF06B-03E1-486E-8319-98EFBD2BC078}">
   <dimension ref="B9:FT67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47226,7 +47226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F327B20C-03B1-4701-A675-7C0B8D6082F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2054A752-1635-4816-88CF-73D2A4240251}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47816,7 +47816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF7D339-9F46-4300-BFFC-2D17B54ACB13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C0A1A7-105D-431D-B621-3280418CD349}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48723,7 +48723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1E6CCF-5E5A-4889-9480-92BFD940AF8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2BCCCE-F64A-4218-95B8-7C975C497F04}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49190,7 +49190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E06B93-8851-4EF7-B7C4-FCAA193BBF92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173D2D00-1357-4655-8499-494B9E931250}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49586,7 +49586,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.18906666666666669</v>
+        <v>0.18906666666666663</v>
       </c>
       <c r="E37" t="s">
         <v>235</v>
@@ -49656,7 +49656,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.11346666666666666</v>
+        <v>0.11346666666666667</v>
       </c>
       <c r="E42" t="s">
         <v>235</v>
@@ -49712,7 +49712,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>9.3833333333333324E-2</v>
+        <v>9.3833333333333338E-2</v>
       </c>
       <c r="E46" t="s">
         <v>235</v>
@@ -49754,7 +49754,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.1643</v>
+        <v>0.16429999999999997</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -49880,7 +49880,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.14710000000000001</v>
+        <v>0.14709999999999998</v>
       </c>
       <c r="E58" t="s">
         <v>235</v>
@@ -50090,7 +50090,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.16716666666666666</v>
+        <v>0.16716666666666669</v>
       </c>
       <c r="E73" t="s">
         <v>235</v>
@@ -50160,7 +50160,7 @@
         <v>45</v>
       </c>
       <c r="D78">
-        <v>0.17656666666666665</v>
+        <v>0.17656666666666668</v>
       </c>
       <c r="E78" t="s">
         <v>235</v>
@@ -50370,7 +50370,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.12953333333333331</v>
+        <v>0.12953333333333333</v>
       </c>
       <c r="E93" t="s">
         <v>235</v>
@@ -50426,7 +50426,7 @@
         <v>43</v>
       </c>
       <c r="D97">
-        <v>0.17906666666666668</v>
+        <v>0.17906666666666671</v>
       </c>
       <c r="E97" t="s">
         <v>235</v>
@@ -50440,7 +50440,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.13753333333333334</v>
+        <v>0.13753333333333331</v>
       </c>
       <c r="E98" t="s">
         <v>235</v>
@@ -50776,7 +50776,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.18909999999999996</v>
+        <v>0.18910000000000002</v>
       </c>
       <c r="E122" t="s">
         <v>235</v>
